--- a/data/credit_bond_2026-09-03.xlsx
+++ b/data/credit_bond_2026-09-03.xlsx
@@ -743,7 +743,7 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/2.0000</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
@@ -1003,7 +1003,11 @@
           <t>7-</t>
         </is>
       </c>
-      <c r="X4" s="3"/>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>2.47%~2.57%</t>
+        </is>
+      </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
           <t>AA+</t>

--- a/data/credit_bond_2026-09-03.xlsx
+++ b/data/credit_bond_2026-09-03.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-09-03" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-09-04" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
     <row r="3" customHeight="true" ht="18.0">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>26桂债03</t>
+          <t>26金源华兴PPN001</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -700,18 +700,14 @@
           <t>09-03 18:00</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>520453.SZ</t>
-        </is>
-      </c>
+      <c r="C3" s="3"/>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>2+2</t>
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>7.0</v>
+        <v>5.0</v>
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="3" t="inlineStr">
@@ -723,37 +719,37 @@
       <c r="I3" s="3"/>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>26桂债02</t>
+          <t>26金源华兴MTN002</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>2.81Y</t>
+          <t>1.68Y+1.00Y</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>2.1474</t>
+          <t>2.1967</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>--/2.0000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>广西金融投资集团有限公司</t>
+          <t>金源华兴融资租赁有限公司</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>B- 35.27</t>
+          <t>D+ 8.64</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -773,46 +769,46 @@
       </c>
       <c r="T3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="U3" s="3"/>
       <c r="V3" s="3"/>
       <c r="W3" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>7-</t>
         </is>
       </c>
       <c r="X3" s="3" t="inlineStr">
         <is>
-          <t>2.21%~2.31%</t>
+          <t>2.47%~2.57%</t>
         </is>
       </c>
       <c r="Y3" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z3" s="3"/>
       <c r="AA3" s="3" t="inlineStr">
         <is>
-          <t>广西壮族自治区</t>
+          <t>江西省-上饶市</t>
         </is>
       </c>
       <c r="AB3" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金拟全部用于偿还有息债务</t>
+          <t>本期债务融资工具基础发行金额为人民币0亿元，发行金额上限为人民币5亿元，扣除发行费用后拟全部用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC3" s="3" t="inlineStr">
         <is>
-          <t>广发证券股份有限公司,中国银河证券股份有限公司,国海证券股份有限公司,中信建投证券股份有限公司,华创证券有限责任公司</t>
+          <t>中信建投证券股份有限公司,江西银行股份有限公司,中信银行股份有限公司,九江银行股份有限公司</t>
         </is>
       </c>
       <c r="AD3" s="3"/>
       <c r="AE3" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF3" s="3" t="inlineStr">
@@ -822,12 +818,12 @@
       </c>
       <c r="AG3" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH3" s="3" t="inlineStr">
         <is>
-          <t>广西金融投资集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+          <t>金源华兴融资租赁有限公司2026年度第一期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI3" s="3" t="inlineStr">
@@ -837,23 +833,23 @@
       </c>
       <c r="AJ3" s="3" t="inlineStr">
         <is>
-          <t>2029-09-07</t>
+          <t>2030-09-04</t>
         </is>
       </c>
       <c r="AK3" s="3"/>
       <c r="AL3" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AM3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AN3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AO3" s="3" t="inlineStr">
@@ -863,7 +859,7 @@
       </c>
       <c r="AP3" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ3" s="3" t="inlineStr">
@@ -873,12 +869,12 @@
       </c>
       <c r="AR3" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS3" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT3" s="3" t="inlineStr">
@@ -888,7 +884,7 @@
       </c>
       <c r="AU3" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2028-09-04</t>
         </is>
       </c>
       <c r="AV3" s="3" t="inlineStr">
@@ -898,7 +894,7 @@
       </c>
       <c r="AW3" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX3" s="3" t="inlineStr">
@@ -916,22 +912,26 @@
     <row r="4" customHeight="true" ht="18.0">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>26金源华兴PPN001</t>
+          <t>26桂债03</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>09-03 18:00</t>
-        </is>
-      </c>
-      <c r="C4" s="3"/>
+          <t>09-03 19:00</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>520453.SZ</t>
+        </is>
+      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>2+2</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3" t="inlineStr">
@@ -939,41 +939,45 @@
           <t>2.00 ~ 2.80</t>
         </is>
       </c>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
+      <c r="H4" s="4" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>87.47</v>
+      </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>26金源华兴MTN002</t>
+          <t>26桂债02</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>1.68Y+1.00Y</t>
+          <t>2.81Y</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>2.1967</t>
+          <t>2.1434</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/2.0000</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>金源华兴融资租赁有限公司</t>
+          <t>广西金融投资集团有限公司</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>C- 10.93</t>
+          <t>C+ 34.31</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -993,46 +997,46 @@
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="U4" s="3"/>
       <c r="V4" s="3"/>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t>2.47%~2.57%</t>
+          <t>2.21%~2.31%</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z4" s="3"/>
       <c r="AA4" s="3" t="inlineStr">
         <is>
-          <t>江西省-上饶市</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="AB4" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具基础发行金额为人民币0亿元，发行金额上限为人民币5亿元，扣除发行费用后拟全部用于偿还有息债务</t>
+          <t>本期债券募集资金拟全部用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC4" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,江西银行股份有限公司,中信银行股份有限公司,九江银行股份有限公司</t>
+          <t>广发证券股份有限公司,中国银河证券股份有限公司,国海证券股份有限公司,中信建投证券股份有限公司,华创证券有限责任公司</t>
         </is>
       </c>
       <c r="AD4" s="3"/>
       <c r="AE4" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF4" s="3" t="inlineStr">
@@ -1042,12 +1046,12 @@
       </c>
       <c r="AG4" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH4" s="3" t="inlineStr">
         <is>
-          <t>金源华兴融资租赁有限公司2026年度第一期定向债务融资工具</t>
+          <t>广西金融投资集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI4" s="3" t="inlineStr">
@@ -1057,25 +1061,25 @@
       </c>
       <c r="AJ4" s="3" t="inlineStr">
         <is>
-          <t>2030-09-04</t>
+          <t>2029-09-07</t>
         </is>
       </c>
       <c r="AK4" s="3"/>
       <c r="AL4" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AN4" s="3" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="AM4" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
           <t>金融</t>
@@ -1083,7 +1087,7 @@
       </c>
       <c r="AP4" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ4" s="3" t="inlineStr">
@@ -1093,12 +1097,12 @@
       </c>
       <c r="AR4" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>金融控股</t>
         </is>
       </c>
       <c r="AS4" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>金融控股</t>
         </is>
       </c>
       <c r="AT4" s="3" t="inlineStr">
@@ -1108,7 +1112,7 @@
       </c>
       <c r="AU4" s="3" t="inlineStr">
         <is>
-          <t>2028-09-04</t>
+          <t/>
         </is>
       </c>
       <c r="AV4" s="3" t="inlineStr">
@@ -1118,7 +1122,7 @@
       </c>
       <c r="AW4" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX4" s="3" t="inlineStr">

--- a/data/credit_bond_2026-09-03.xlsx
+++ b/data/credit_bond_2026-09-03.xlsx
@@ -715,8 +715,12 @@
           <t>2.00 ~ 2.80</t>
         </is>
       </c>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+      <c r="H3" s="4" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>91.59</v>
+      </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
           <t>2.22</t>
@@ -772,8 +776,12 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U3" s="3"/>
-      <c r="V3" s="3"/>
+      <c r="U3" s="4" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="V3" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W3" s="3" t="inlineStr">
         <is>
           <t>7-</t>

--- a/data/credit_bond_2026-09-03.xlsx
+++ b/data/credit_bond_2026-09-03.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-09-04" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-09-07" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,11 @@
           <t>09-03 18:00</t>
         </is>
       </c>
-      <c r="C3" s="3"/>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>032680515.IB</t>
+        </is>
+      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
           <t>2+2</t>
@@ -709,7 +713,9 @@
       <c r="E3" s="4" t="n">
         <v>5.0</v>
       </c>
-      <c r="F3" s="3"/>
+      <c r="F3" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
           <t>2.00 ~ 2.80</t>
@@ -753,7 +759,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>D+ 8.64</t>
+          <t>D+ 7.91</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -985,7 +991,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.31</t>
+          <t>B- 36.30</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">

--- a/data/credit_bond_2026-09-03.xlsx
+++ b/data/credit_bond_2026-09-03.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-09-07" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-09-08" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>D+ 7.91</t>
+          <t>D+ 7.04</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -947,7 +947,9 @@
       <c r="E4" s="4" t="n">
         <v>7.0</v>
       </c>
-      <c r="F4" s="3"/>
+      <c r="F4" s="4" t="n">
+        <v>7.0</v>
+      </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
           <t>2.00 ~ 2.80</t>
@@ -991,7 +993,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>B- 36.30</t>
+          <t>B- 35.64</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -1014,7 +1016,9 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="U4" s="3"/>
+      <c r="U4" s="4" t="n">
+        <v>3.16</v>
+      </c>
       <c r="V4" s="3"/>
       <c r="W4" s="3" t="inlineStr">
         <is>

--- a/data/credit_bond_2026-09-03.xlsx
+++ b/data/credit_bond_2026-09-03.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-09-08" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-09-09" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>D+ 7.04</t>
+          <t>D+ 9.14</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>B- 35.64</t>
+          <t>B- 37.38</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
